--- a/templates/template_horeca_products.xlsx
+++ b/templates/template_horeca_products.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simaple_form" sheetId="1" r:id="Rf07572c5f2c94331"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simaple_form" sheetId="1" r:id="Re720ac98e4054b83"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -91,24 +91,6 @@
     <x:t xml:space="preserve">WURKZ</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">DAZZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DAZZ Zero Sugar</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">EXPREZ Can 330ml</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">EXPREZ Melon</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CAMBODIA Sport 300mL</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CAMBODIA Sport 500mL</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">CAMBODIA WATER 500mL</x:t>
   </x:si>
   <x:si>
@@ -196,12 +178,6 @@
     <x:t xml:space="preserve">V Cola 330ml</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Boostrong</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Krud ED</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">BACCHUSE</x:t>
   </x:si>
   <x:si>
@@ -209,9 +185,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">BACCHUSE Sugar Free</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Idol Can 330ml</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Sting Can 330ml</x:t>
@@ -459,13 +432,13 @@
     <xdr:ext cx="809625" cy="809625"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="/xl/media/image1.png"/>
+        <xdr:cNvPr id="1" name="/xl/media/image.png"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Re9a5d853b4774e9c"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra950d79a19d74cbf"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1191,8 +1164,8 @@
       <x:c r="A17" s="3">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B17" s="1" t="s">
-        <x:v>27</x:v>
+      <x:c r="B17" s="1" t="str">
+        <x:v>DAZZ ORD</x:v>
       </x:c>
       <x:c r="C17" s="12"/>
       <x:c r="D17" s="13"/>
@@ -1224,8 +1197,8 @@
       <x:c r="A18" s="3">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B18" s="1" t="s">
-        <x:v>28</x:v>
+      <x:c r="B18" s="1" t="str">
+        <x:v>DAZZ Zero Sugar ORD</x:v>
       </x:c>
       <x:c r="C18" s="12"/>
       <x:c r="D18" s="13"/>
@@ -1257,8 +1230,8 @@
       <x:c r="A19" s="3">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B19" s="1" t="s">
-        <x:v>29</x:v>
+      <x:c r="B19" s="1" t="str">
+        <x:v>EXPREZ Can 330ml ORD</x:v>
       </x:c>
       <x:c r="C19" s="12"/>
       <x:c r="D19" s="13"/>
@@ -1290,8 +1263,8 @@
       <x:c r="A20" s="3">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B20" s="1" t="s">
-        <x:v>30</x:v>
+      <x:c r="B20" s="1" t="str">
+        <x:v>EXPREZ Melon ORD</x:v>
       </x:c>
       <x:c r="C20" s="12"/>
       <x:c r="D20" s="13"/>
@@ -1323,9 +1296,7 @@
       <x:c r="A21" s="3">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B21" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="B21" s="1"/>
       <x:c r="C21" s="12"/>
       <x:c r="D21" s="13"/>
       <x:c r="E21" s="13"/>
@@ -1356,8 +1327,8 @@
       <x:c r="A22" s="3">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B22" s="1" t="s">
-        <x:v>32</x:v>
+      <x:c r="B22" s="1" t="str">
+        <x:v>CAMBODIA Sport 500mL ORD</x:v>
       </x:c>
       <x:c r="C22" s="12"/>
       <x:c r="D22" s="13"/>
@@ -1390,7 +1361,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C23" s="12"/>
       <x:c r="D23" s="13"/>
@@ -1420,7 +1391,7 @@
     </x:row>
     <x:row r="24" ht="30" customHeight="1">
       <x:c r="A24" s="18" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B24" s="11"/>
       <x:c r="C24" s="11"/>
@@ -1451,85 +1422,85 @@
     </x:row>
     <x:row r="25" ht="30" customHeight="1">
       <x:c r="A25" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B25" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C25" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D25" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E25" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F25" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G25" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H25" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="I25" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J25" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="K25" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L25" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="M25" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="N25" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O25" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="P25" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="Q25" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="R25" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="S25" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="T25" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="U25" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="V25" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="W25" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="X25" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="Y25" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="Z25" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="AA25" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="30" customHeight="1">
@@ -1545,14 +1516,14 @@
       <x:c r="F26" s="3"/>
       <x:c r="G26" s="3"/>
       <x:c r="H26" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I26" s="3"/>
       <x:c r="J26" s="3"/>
       <x:c r="K26" s="3"/>
       <x:c r="L26" s="3"/>
       <x:c r="M26" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="N26" s="3"/>
       <x:c r="O26" s="3"/>
@@ -1589,21 +1560,21 @@
       <x:c r="K27" s="3"/>
       <x:c r="L27" s="3"/>
       <x:c r="M27" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="N27" s="3"/>
       <x:c r="O27" s="3"/>
       <x:c r="P27" s="3"/>
       <x:c r="Q27" s="3"/>
       <x:c r="R27" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="S27" s="3"/>
       <x:c r="T27" s="3"/>
       <x:c r="U27" s="3"/>
       <x:c r="V27" s="3"/>
       <x:c r="W27" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="X27" s="3"/>
       <x:c r="Y27" s="3"/>
@@ -1623,21 +1594,21 @@
       <x:c r="F28" s="3"/>
       <x:c r="G28" s="3"/>
       <x:c r="H28" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I28" s="3"/>
       <x:c r="J28" s="3"/>
       <x:c r="K28" s="3"/>
       <x:c r="L28" s="3"/>
       <x:c r="M28" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="N28" s="3"/>
       <x:c r="O28" s="3"/>
       <x:c r="P28" s="3"/>
       <x:c r="Q28" s="3"/>
       <x:c r="R28" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="S28" s="3"/>
       <x:c r="T28" s="3"/>
@@ -1662,21 +1633,21 @@
       <x:c r="F29" s="3"/>
       <x:c r="G29" s="3"/>
       <x:c r="H29" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="I29" s="3"/>
       <x:c r="J29" s="3"/>
       <x:c r="K29" s="3"/>
       <x:c r="L29" s="3"/>
       <x:c r="M29" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N29" s="3"/>
       <x:c r="O29" s="3"/>
       <x:c r="P29" s="3"/>
       <x:c r="Q29" s="3"/>
       <x:c r="R29" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="S29" s="3"/>
       <x:c r="T29" s="3"/>
@@ -1708,14 +1679,14 @@
       <x:c r="K30" s="3"/>
       <x:c r="L30" s="3"/>
       <x:c r="M30" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N30" s="3"/>
       <x:c r="O30" s="3"/>
       <x:c r="P30" s="3"/>
       <x:c r="Q30" s="3"/>
       <x:c r="R30" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="S30" s="3"/>
       <x:c r="T30" s="3"/>
@@ -1732,7 +1703,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C31" s="3"/>
       <x:c r="D31" s="3"/>
@@ -1740,28 +1711,28 @@
       <x:c r="F31" s="3"/>
       <x:c r="G31" s="3"/>
       <x:c r="H31" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I31" s="3"/>
       <x:c r="J31" s="3"/>
       <x:c r="K31" s="3"/>
       <x:c r="L31" s="3"/>
       <x:c r="M31" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="N31" s="3"/>
       <x:c r="O31" s="3"/>
       <x:c r="P31" s="3"/>
       <x:c r="Q31" s="3"/>
       <x:c r="R31" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="S31" s="3"/>
       <x:c r="T31" s="3"/>
       <x:c r="U31" s="3"/>
       <x:c r="V31" s="3"/>
       <x:c r="W31" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="X31" s="3"/>
       <x:c r="Y31" s="3"/>
@@ -1781,7 +1752,7 @@
       <x:c r="F32" s="3"/>
       <x:c r="G32" s="3"/>
       <x:c r="H32" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I32" s="3"/>
       <x:c r="J32" s="3"/>
@@ -1816,14 +1787,14 @@
       <x:c r="F33" s="3"/>
       <x:c r="G33" s="3"/>
       <x:c r="H33" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I33" s="3"/>
       <x:c r="J33" s="3"/>
       <x:c r="K33" s="3"/>
       <x:c r="L33" s="3"/>
       <x:c r="M33" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="N33" s="3"/>
       <x:c r="O33" s="3"/>
@@ -1852,8 +1823,8 @@
       <x:c r="E34" s="3"/>
       <x:c r="F34" s="3"/>
       <x:c r="G34" s="3"/>
-      <x:c r="H34" s="1" t="s">
-        <x:v>62</x:v>
+      <x:c r="H34" s="1" t="str">
+        <x:v>Boostrong ORD</x:v>
       </x:c>
       <x:c r="I34" s="3"/>
       <x:c r="J34" s="3"/>
@@ -1864,8 +1835,8 @@
       <x:c r="O34" s="3"/>
       <x:c r="P34" s="3"/>
       <x:c r="Q34" s="3"/>
-      <x:c r="R34" s="1" t="s">
-        <x:v>63</x:v>
+      <x:c r="R34" s="1" t="str">
+        <x:v>Krud ED ORD</x:v>
       </x:c>
       <x:c r="S34" s="3"/>
       <x:c r="T34" s="3"/>
@@ -1881,8 +1852,8 @@
       <x:c r="A35" s="3">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B35" s="1" t="s">
-        <x:v>27</x:v>
+      <x:c r="B35" s="1" t="str">
+        <x:v>DAZZ ORD</x:v>
       </x:c>
       <x:c r="C35" s="3"/>
       <x:c r="D35" s="3"/>
@@ -1890,7 +1861,7 @@
       <x:c r="F35" s="3"/>
       <x:c r="G35" s="3"/>
       <x:c r="H35" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I35" s="3"/>
       <x:c r="J35" s="3"/>
@@ -1902,7 +1873,7 @@
       <x:c r="P35" s="3"/>
       <x:c r="Q35" s="3"/>
       <x:c r="R35" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="S35" s="3"/>
       <x:c r="T35" s="3"/>
@@ -1918,8 +1889,8 @@
       <x:c r="A36" s="3">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B36" s="1" t="s">
-        <x:v>28</x:v>
+      <x:c r="B36" s="1" t="str">
+        <x:v>DAZZ Zero Sugar ORD</x:v>
       </x:c>
       <x:c r="C36" s="3"/>
       <x:c r="D36" s="3"/>
@@ -1927,7 +1898,7 @@
       <x:c r="F36" s="3"/>
       <x:c r="G36" s="3"/>
       <x:c r="H36" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I36" s="3"/>
       <x:c r="J36" s="3"/>
@@ -1953,30 +1924,30 @@
       <x:c r="A37" s="3">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B37" s="1" t="s">
-        <x:v>29</x:v>
+      <x:c r="B37" s="1" t="str">
+        <x:v>EXPREZ Can 330ml ORD</x:v>
       </x:c>
       <x:c r="C37" s="3"/>
       <x:c r="D37" s="3"/>
       <x:c r="E37" s="3"/>
       <x:c r="F37" s="3"/>
       <x:c r="G37" s="3"/>
-      <x:c r="H37" s="1" t="s">
-        <x:v>30</x:v>
+      <x:c r="H37" s="1" t="str">
+        <x:v>EXPREZ Melon ORD</x:v>
       </x:c>
       <x:c r="I37" s="3"/>
       <x:c r="J37" s="3"/>
       <x:c r="K37" s="3"/>
       <x:c r="L37" s="3"/>
-      <x:c r="M37" s="1" t="s">
-        <x:v>67</x:v>
+      <x:c r="M37" s="1" t="str">
+        <x:v>Idol Can 330ml ORD</x:v>
       </x:c>
       <x:c r="N37" s="3"/>
       <x:c r="O37" s="3"/>
       <x:c r="P37" s="3"/>
       <x:c r="Q37" s="3"/>
       <x:c r="R37" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="S37" s="3"/>
       <x:c r="T37" s="3"/>
@@ -1992,30 +1963,28 @@
       <x:c r="A38" s="3">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B38" s="1" t="s">
-        <x:v>32</x:v>
+      <x:c r="B38" s="1" t="str">
+        <x:v>CAMBODIA Sport 500mL ORD</x:v>
       </x:c>
       <x:c r="C38" s="3"/>
       <x:c r="D38" s="3"/>
       <x:c r="E38" s="3"/>
       <x:c r="F38" s="3"/>
       <x:c r="G38" s="3"/>
-      <x:c r="H38" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="H38" s="1"/>
       <x:c r="I38" s="3"/>
       <x:c r="J38" s="3"/>
       <x:c r="K38" s="3"/>
       <x:c r="L38" s="3"/>
       <x:c r="M38" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="N38" s="3"/>
       <x:c r="O38" s="3"/>
       <x:c r="P38" s="3"/>
       <x:c r="Q38" s="3"/>
       <x:c r="R38" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="S38" s="3"/>
       <x:c r="T38" s="3"/>
@@ -2032,7 +2001,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C39" s="3"/>
       <x:c r="D39" s="3"/>
@@ -2040,28 +2009,28 @@
       <x:c r="F39" s="3"/>
       <x:c r="G39" s="3"/>
       <x:c r="H39" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I39" s="3"/>
       <x:c r="J39" s="3"/>
       <x:c r="K39" s="3"/>
       <x:c r="L39" s="3"/>
       <x:c r="M39" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="N39" s="3"/>
       <x:c r="O39" s="3"/>
       <x:c r="P39" s="3"/>
       <x:c r="Q39" s="3"/>
       <x:c r="R39" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="S39" s="3"/>
       <x:c r="T39" s="3"/>
       <x:c r="U39" s="3"/>
       <x:c r="V39" s="3"/>
       <x:c r="W39" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="X39" s="3"/>
       <x:c r="Y39" s="3"/>
@@ -2085,7 +2054,7 @@
       <x:c r="F41" s="22"/>
       <x:c r="G41" s="14"/>
       <x:c r="I41" s="23" t="s">
-        <x:v>75</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J41" s="11"/>
       <x:c r="K41" s="11"/>
@@ -2096,7 +2065,7 @@
       <x:c r="P41" s="11"/>
       <x:c r="Q41" s="11"/>
       <x:c r="S41" s="23" t="s">
-        <x:v>76</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="T41" s="11"/>
       <x:c r="U41" s="11"/>
@@ -2147,7 +2116,7 @@
       <x:c r="F43" s="12"/>
       <x:c r="G43" s="14"/>
       <x:c r="I43" s="18" t="s">
-        <x:v>77</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="J43" s="11"/>
       <x:c r="K43" s="11"/>
@@ -2178,7 +2147,7 @@
       <x:c r="F44" s="21"/>
       <x:c r="G44" s="11"/>
       <x:c r="I44" s="18" t="s">
-        <x:v>78</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="J44" s="11"/>
       <x:c r="K44" s="11"/>
@@ -2209,7 +2178,7 @@
       <x:c r="F45" s="21"/>
       <x:c r="G45" s="11"/>
       <x:c r="I45" s="18" t="s">
-        <x:v>79</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J45" s="11"/>
       <x:c r="K45" s="11"/>
@@ -2220,7 +2189,7 @@
       <x:c r="P45" s="11"/>
       <x:c r="Q45" s="11"/>
       <x:c r="S45" s="18" t="s">
-        <x:v>79</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="T45" s="11"/>
       <x:c r="U45" s="11"/>
@@ -2367,6 +2336,6 @@
     <x:mergeCell ref="A45:G45"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5719dfee14f45da"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7088b02181bd4a32"/>
 </x:worksheet>
 </file>
--- a/templates/template_horeca_products.xlsx
+++ b/templates/template_horeca_products.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simaple_form" sheetId="1" r:id="Re720ac98e4054b83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simaple_form" sheetId="1" r:id="R1f6ad4ce256d4172"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -88,9 +88,6 @@
     <x:t xml:space="preserve">CAMBODIA COLA</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">WURKZ</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">CAMBODIA WATER 500mL</x:t>
   </x:si>
   <x:si>
@@ -179,9 +176,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">BACCHUSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Dragon</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">BACCHUSE Sugar Free</x:t>
@@ -438,7 +432,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra950d79a19d74cbf"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rac8034e16006435a"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1131,8 +1125,8 @@
       <x:c r="A16" s="3">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B16" s="1" t="s">
-        <x:v>26</x:v>
+      <x:c r="B16" s="1" t="str">
+        <x:v>WURKZ ORD</x:v>
       </x:c>
       <x:c r="C16" s="12"/>
       <x:c r="D16" s="13"/>
@@ -1361,7 +1355,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C23" s="12"/>
       <x:c r="D23" s="13"/>
@@ -1391,7 +1385,7 @@
     </x:row>
     <x:row r="24" ht="30" customHeight="1">
       <x:c r="A24" s="18" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B24" s="11"/>
       <x:c r="C24" s="11"/>
@@ -1422,85 +1416,85 @@
     </x:row>
     <x:row r="25" ht="30" customHeight="1">
       <x:c r="A25" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B25" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C25" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D25" s="4" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D25" s="4" t="s">
+      <x:c r="E25" s="4" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="E25" s="4" t="s">
+      <x:c r="F25" s="4" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="F25" s="4" t="s">
+      <x:c r="G25" s="4" t="s">
         <x:v>33</x:v>
-      </x:c>
-      <x:c r="G25" s="4" t="s">
-        <x:v>34</x:v>
       </x:c>
       <x:c r="H25" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="I25" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="J25" s="4" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="J25" s="4" t="s">
+      <x:c r="K25" s="4" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="K25" s="4" t="s">
+      <x:c r="L25" s="4" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="L25" s="4" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="M25" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="N25" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="O25" s="4" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="O25" s="4" t="s">
+      <x:c r="P25" s="4" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="P25" s="4" t="s">
+      <x:c r="Q25" s="4" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="Q25" s="4" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="R25" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="S25" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="T25" s="4" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="T25" s="4" t="s">
+      <x:c r="U25" s="4" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="U25" s="4" t="s">
+      <x:c r="V25" s="4" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="V25" s="4" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="W25" s="4" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="X25" s="4" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="Y25" s="4" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="Y25" s="4" t="s">
+      <x:c r="Z25" s="4" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="Z25" s="4" t="s">
+      <x:c r="AA25" s="4" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="AA25" s="4" t="s">
-        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="30" customHeight="1">
@@ -1516,14 +1510,14 @@
       <x:c r="F26" s="3"/>
       <x:c r="G26" s="3"/>
       <x:c r="H26" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="I26" s="3"/>
       <x:c r="J26" s="3"/>
       <x:c r="K26" s="3"/>
       <x:c r="L26" s="3"/>
       <x:c r="M26" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="N26" s="3"/>
       <x:c r="O26" s="3"/>
@@ -1560,21 +1554,21 @@
       <x:c r="K27" s="3"/>
       <x:c r="L27" s="3"/>
       <x:c r="M27" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="N27" s="3"/>
       <x:c r="O27" s="3"/>
       <x:c r="P27" s="3"/>
       <x:c r="Q27" s="3"/>
       <x:c r="R27" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="S27" s="3"/>
       <x:c r="T27" s="3"/>
       <x:c r="U27" s="3"/>
       <x:c r="V27" s="3"/>
       <x:c r="W27" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="X27" s="3"/>
       <x:c r="Y27" s="3"/>
@@ -1594,21 +1588,21 @@
       <x:c r="F28" s="3"/>
       <x:c r="G28" s="3"/>
       <x:c r="H28" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I28" s="3"/>
       <x:c r="J28" s="3"/>
       <x:c r="K28" s="3"/>
       <x:c r="L28" s="3"/>
       <x:c r="M28" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="N28" s="3"/>
       <x:c r="O28" s="3"/>
       <x:c r="P28" s="3"/>
       <x:c r="Q28" s="3"/>
       <x:c r="R28" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="S28" s="3"/>
       <x:c r="T28" s="3"/>
@@ -1633,21 +1627,21 @@
       <x:c r="F29" s="3"/>
       <x:c r="G29" s="3"/>
       <x:c r="H29" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="I29" s="3"/>
       <x:c r="J29" s="3"/>
       <x:c r="K29" s="3"/>
       <x:c r="L29" s="3"/>
       <x:c r="M29" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="N29" s="3"/>
       <x:c r="O29" s="3"/>
       <x:c r="P29" s="3"/>
       <x:c r="Q29" s="3"/>
       <x:c r="R29" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="S29" s="3"/>
       <x:c r="T29" s="3"/>
@@ -1679,14 +1673,14 @@
       <x:c r="K30" s="3"/>
       <x:c r="L30" s="3"/>
       <x:c r="M30" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N30" s="3"/>
       <x:c r="O30" s="3"/>
       <x:c r="P30" s="3"/>
       <x:c r="Q30" s="3"/>
       <x:c r="R30" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="S30" s="3"/>
       <x:c r="T30" s="3"/>
@@ -1703,7 +1697,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C31" s="3"/>
       <x:c r="D31" s="3"/>
@@ -1711,28 +1705,28 @@
       <x:c r="F31" s="3"/>
       <x:c r="G31" s="3"/>
       <x:c r="H31" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I31" s="3"/>
       <x:c r="J31" s="3"/>
       <x:c r="K31" s="3"/>
       <x:c r="L31" s="3"/>
       <x:c r="M31" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N31" s="3"/>
       <x:c r="O31" s="3"/>
       <x:c r="P31" s="3"/>
       <x:c r="Q31" s="3"/>
       <x:c r="R31" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="S31" s="3"/>
       <x:c r="T31" s="3"/>
       <x:c r="U31" s="3"/>
       <x:c r="V31" s="3"/>
       <x:c r="W31" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="X31" s="3"/>
       <x:c r="Y31" s="3"/>
@@ -1752,7 +1746,7 @@
       <x:c r="F32" s="3"/>
       <x:c r="G32" s="3"/>
       <x:c r="H32" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="I32" s="3"/>
       <x:c r="J32" s="3"/>
@@ -1787,14 +1781,14 @@
       <x:c r="F33" s="3"/>
       <x:c r="G33" s="3"/>
       <x:c r="H33" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I33" s="3"/>
       <x:c r="J33" s="3"/>
       <x:c r="K33" s="3"/>
       <x:c r="L33" s="3"/>
       <x:c r="M33" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="N33" s="3"/>
       <x:c r="O33" s="3"/>
@@ -1815,8 +1809,8 @@
       <x:c r="A34" s="3">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B34" s="1" t="s">
-        <x:v>26</x:v>
+      <x:c r="B34" s="1" t="str">
+        <x:v>WURKZ ORD</x:v>
       </x:c>
       <x:c r="C34" s="3"/>
       <x:c r="D34" s="3"/>
@@ -1861,7 +1855,7 @@
       <x:c r="F35" s="3"/>
       <x:c r="G35" s="3"/>
       <x:c r="H35" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="I35" s="3"/>
       <x:c r="J35" s="3"/>
@@ -1872,8 +1866,8 @@
       <x:c r="O35" s="3"/>
       <x:c r="P35" s="3"/>
       <x:c r="Q35" s="3"/>
-      <x:c r="R35" s="1" t="s">
-        <x:v>57</x:v>
+      <x:c r="R35" s="1" t="str">
+        <x:v>Dragon ORD</x:v>
       </x:c>
       <x:c r="S35" s="3"/>
       <x:c r="T35" s="3"/>
@@ -1898,7 +1892,7 @@
       <x:c r="F36" s="3"/>
       <x:c r="G36" s="3"/>
       <x:c r="H36" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I36" s="3"/>
       <x:c r="J36" s="3"/>
@@ -1947,7 +1941,7 @@
       <x:c r="P37" s="3"/>
       <x:c r="Q37" s="3"/>
       <x:c r="R37" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="S37" s="3"/>
       <x:c r="T37" s="3"/>
@@ -1977,14 +1971,14 @@
       <x:c r="K38" s="3"/>
       <x:c r="L38" s="3"/>
       <x:c r="M38" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N38" s="3"/>
       <x:c r="O38" s="3"/>
       <x:c r="P38" s="3"/>
       <x:c r="Q38" s="3"/>
       <x:c r="R38" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="S38" s="3"/>
       <x:c r="T38" s="3"/>
@@ -2001,7 +1995,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C39" s="3"/>
       <x:c r="D39" s="3"/>
@@ -2009,28 +2003,28 @@
       <x:c r="F39" s="3"/>
       <x:c r="G39" s="3"/>
       <x:c r="H39" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I39" s="3"/>
       <x:c r="J39" s="3"/>
       <x:c r="K39" s="3"/>
       <x:c r="L39" s="3"/>
       <x:c r="M39" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="N39" s="3"/>
       <x:c r="O39" s="3"/>
       <x:c r="P39" s="3"/>
       <x:c r="Q39" s="3"/>
       <x:c r="R39" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="S39" s="3"/>
       <x:c r="T39" s="3"/>
       <x:c r="U39" s="3"/>
       <x:c r="V39" s="3"/>
       <x:c r="W39" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="X39" s="3"/>
       <x:c r="Y39" s="3"/>
@@ -2054,7 +2048,7 @@
       <x:c r="F41" s="22"/>
       <x:c r="G41" s="14"/>
       <x:c r="I41" s="23" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J41" s="11"/>
       <x:c r="K41" s="11"/>
@@ -2065,7 +2059,7 @@
       <x:c r="P41" s="11"/>
       <x:c r="Q41" s="11"/>
       <x:c r="S41" s="23" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="T41" s="11"/>
       <x:c r="U41" s="11"/>
@@ -2116,7 +2110,7 @@
       <x:c r="F43" s="12"/>
       <x:c r="G43" s="14"/>
       <x:c r="I43" s="18" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="J43" s="11"/>
       <x:c r="K43" s="11"/>
@@ -2147,7 +2141,7 @@
       <x:c r="F44" s="21"/>
       <x:c r="G44" s="11"/>
       <x:c r="I44" s="18" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="J44" s="11"/>
       <x:c r="K44" s="11"/>
@@ -2178,7 +2172,7 @@
       <x:c r="F45" s="21"/>
       <x:c r="G45" s="11"/>
       <x:c r="I45" s="18" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="J45" s="11"/>
       <x:c r="K45" s="11"/>
@@ -2189,7 +2183,7 @@
       <x:c r="P45" s="11"/>
       <x:c r="Q45" s="11"/>
       <x:c r="S45" s="18" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="T45" s="11"/>
       <x:c r="U45" s="11"/>
@@ -2336,6 +2330,6 @@
     <x:mergeCell ref="A45:G45"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7088b02181bd4a32"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4982dccb34a34002"/>
 </x:worksheet>
 </file>